--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12330"/>
+    <workbookView windowWidth="25200" windowHeight="12090"/>
   </bookViews>
   <sheets>
     <sheet name="Doing" sheetId="1" r:id="rId1"/>
@@ -1189,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1269,6 +1269,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1590,21 +1593,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="5.58181818181818" customWidth="1"/>
-    <col min="3" max="3" width="11.1818181818182" customWidth="1"/>
+    <col min="1" max="2" width="5.58333333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.1833333333333" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="20.8181818181818" customWidth="1"/>
+    <col min="5" max="5" width="20.8166666666667" customWidth="1"/>
     <col min="6" max="6" width="7.5" customWidth="1"/>
-    <col min="7" max="7" width="26.5454545454545" customWidth="1"/>
-    <col min="8" max="8" width="9.87272727272727" customWidth="1"/>
-    <col min="9" max="9" width="9.12727272727273" customWidth="1"/>
-    <col min="10" max="10" width="10.8363636363636" customWidth="1"/>
+    <col min="7" max="7" width="26.5416666666667" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="9" width="9.125" customWidth="1"/>
+    <col min="10" max="10" width="10.8333333333333" customWidth="1"/>
     <col min="11" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15.75" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1669,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15" spans="1:17">
+    <row r="2" customFormat="1" ht="15.75" spans="1:18">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1718,13 +1721,16 @@
       <c r="Q2" s="21">
         <v>46046</v>
       </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15"/>
-    <row r="12" s="2" customFormat="1" ht="15"/>
-    <row r="13" s="2" customFormat="1" ht="15"/>
-    <row r="14" s="2" customFormat="1" ht="15"/>
-    <row r="15" s="2" customFormat="1" ht="15"/>
-    <row r="16" s="2" customFormat="1" ht="15" spans="1:9">
+      <c r="R2" s="30">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="15.75"/>
+    <row r="12" s="2" customFormat="1" ht="15.75"/>
+    <row r="13" s="2" customFormat="1" ht="15.75"/>
+    <row r="14" s="2" customFormat="1" ht="15.75"/>
+    <row r="15" s="2" customFormat="1" ht="15.75"/>
+    <row r="16" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -1735,7 +1741,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="15" spans="1:9">
+    <row r="17" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -1746,7 +1752,7 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" ht="17.5" spans="2:13">
+    <row r="18" ht="18.75" spans="2:13">
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
@@ -1762,7 +1768,7 @@
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" ht="17.5" spans="2:13">
+    <row r="19" ht="18.75" spans="2:13">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1776,7 +1782,7 @@
       <c r="L19" s="29"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" ht="17.5" spans="2:12">
+    <row r="20" ht="18.75" spans="2:12">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1788,7 +1794,7 @@
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" ht="17.5" spans="2:13">
+    <row r="21" ht="18.75" spans="2:13">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1802,7 +1808,7 @@
       <c r="L21" s="29"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" ht="17.5" spans="2:13">
+    <row r="22" ht="18.75" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1830,22 +1836,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="4.58181818181818" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="17.7272727272727" customWidth="1"/>
-    <col min="5" max="5" width="23.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="7.33636363636364" customWidth="1"/>
-    <col min="7" max="7" width="27.1272727272727" customWidth="1"/>
-    <col min="8" max="9" width="9.58181818181818" customWidth="1"/>
-    <col min="10" max="10" width="10.6272727272727" customWidth="1"/>
-    <col min="11" max="20" width="11.2727272727273" customWidth="1"/>
-    <col min="21" max="21" width="10.7545454545455" customWidth="1"/>
+    <col min="1" max="2" width="4.58333333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="17.725" customWidth="1"/>
+    <col min="5" max="5" width="23.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.33333333333333" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
+    <col min="8" max="9" width="9.58333333333333" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="20" width="11.275" customWidth="1"/>
+    <col min="21" max="21" width="10.7583333333333" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:21">
+    <row r="1" ht="15.75" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1910,7 +1916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15" spans="1:21">
+    <row r="2" customFormat="1" ht="15.75" spans="1:21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1975,7 +1981,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="15" spans="1:19">
+    <row r="3" customFormat="1" ht="15.75" spans="1:19">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -2034,7 +2040,7 @@
         <v>45304</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="15" spans="1:11">
+    <row r="4" customFormat="1" ht="15.75" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -2069,7 +2075,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="15" spans="1:20">
+    <row r="5" customFormat="1" ht="15.75" spans="1:20">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -2129,7 +2135,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" customFormat="1" ht="15" spans="1:20">
+    <row r="6" customFormat="1" ht="15.75" spans="1:20">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -2191,7 +2197,7 @@
         <v>45344</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="15" spans="1:20">
+    <row r="7" customFormat="1" ht="15.75" spans="1:20">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -2278,7 +2284,7 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="15" spans="1:20">
+    <row r="9" customFormat="1" ht="15.75" spans="1:20">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -2340,7 +2346,7 @@
         <v>45263</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="15" spans="1:20">
+    <row r="10" customFormat="1" ht="15.75" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2382,7 +2388,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="15" spans="1:20">
+    <row r="11" customFormat="1" ht="15.75" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2424,7 +2430,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="15" spans="1:20">
+    <row r="12" customFormat="1" ht="15.75" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2448,7 +2454,7 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="1" ht="15" spans="1:20">
+    <row r="13" customFormat="1" ht="15.75" spans="1:20">
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
@@ -2510,7 +2516,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="15" spans="1:20">
+    <row r="14" customFormat="1" ht="15.75" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2534,7 +2540,7 @@
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" customFormat="1" ht="15" spans="1:20">
+    <row r="15" customFormat="1" ht="15.75" spans="1:20">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -2590,7 +2596,7 @@
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" customFormat="1" ht="15" spans="1:20">
+    <row r="16" customFormat="1" ht="15.75" spans="1:20">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -2652,7 +2658,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="15" spans="1:20">
+    <row r="17" customFormat="1" ht="15.75" spans="1:20">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -2714,7 +2720,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="15" spans="1:20">
+    <row r="18" customFormat="1" ht="15.75" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2746,7 +2752,7 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
     </row>
-    <row r="19" customFormat="1" ht="15" spans="1:20">
+    <row r="19" customFormat="1" ht="15.75" spans="1:20">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -2808,7 +2814,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="15" spans="1:20">
+    <row r="20" customFormat="1" ht="15.75" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2840,7 +2846,7 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
     </row>
-    <row r="21" customFormat="1" ht="15" spans="1:20">
+    <row r="21" customFormat="1" ht="15.75" spans="1:20">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -2902,7 +2908,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="15" spans="1:20">
+    <row r="22" customFormat="1" ht="15.75" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2944,7 +2950,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="15" spans="1:20">
+    <row r="23" customFormat="1" ht="15.75" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2976,7 +2982,7 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="15" spans="1:20">
+    <row r="24" customFormat="1" ht="15.75" spans="1:20">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
@@ -3038,7 +3044,7 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="15" spans="1:20">
+    <row r="25" customFormat="1" ht="15.75" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3080,7 +3086,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="15" spans="1:20">
+    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3118,7 +3124,7 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
     </row>
-    <row r="27" customFormat="1" ht="15" spans="1:20">
+    <row r="27" customFormat="1" ht="15.75" spans="1:20">
       <c r="A27" s="6" t="s">
         <v>103</v>
       </c>
@@ -3162,7 +3168,7 @@
       <c r="S27" s="25"/>
       <c r="T27" s="25"/>
     </row>
-    <row r="28" customFormat="1" ht="15" spans="1:20">
+    <row r="28" customFormat="1" ht="15.75" spans="1:20">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -3216,7 +3222,7 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
     </row>
-    <row r="29" customFormat="1" ht="15" spans="1:18">
+    <row r="29" customFormat="1" ht="15.75" spans="1:18">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -3258,7 +3264,7 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
     </row>
-    <row r="30" customFormat="1" ht="15" spans="1:20">
+    <row r="30" customFormat="1" ht="15.75" spans="1:20">
       <c r="A30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3312,7 +3318,7 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" customFormat="1" ht="15" spans="1:20">
+    <row r="31" customFormat="1" ht="15.75" spans="1:20">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -3374,7 +3380,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="15" spans="1:20">
+    <row r="32" customFormat="1" ht="15.75" spans="1:20">
       <c r="A32" s="5" t="s">
         <v>20</v>
       </c>
@@ -3436,7 +3442,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="15" spans="1:20">
+    <row r="33" customFormat="1" ht="15.75" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3464,7 +3470,7 @@
       <c r="S33" s="22"/>
       <c r="T33" s="22"/>
     </row>
-    <row r="34" customFormat="1" ht="15" spans="1:20">
+    <row r="34" customFormat="1" ht="15.75" spans="1:20">
       <c r="A34" s="6" t="s">
         <v>20</v>
       </c>
@@ -3520,7 +3526,7 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
     </row>
-    <row r="35" customFormat="1" ht="15" spans="1:20">
+    <row r="35" customFormat="1" ht="15.75" spans="1:20">
       <c r="A35" s="5" t="s">
         <v>20</v>
       </c>
@@ -3582,7 +3588,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="15" spans="1:20">
+    <row r="36" customFormat="1" ht="15.75" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3624,7 +3630,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="15" spans="1:20">
+    <row r="37" customFormat="1" ht="15.75" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3666,7 +3672,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="15" spans="1:20">
+    <row r="38" customFormat="1" ht="15.75" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3695,7 +3701,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" customFormat="1" ht="15" spans="1:20">
+    <row r="39" customFormat="1" ht="15.75" spans="1:20">
       <c r="A39" s="5" t="s">
         <v>20</v>
       </c>
@@ -3757,7 +3763,7 @@
         <v>45592</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="15" spans="1:20">
+    <row r="40" customFormat="1" ht="15.75" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3799,7 +3805,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="15" spans="1:13">
+    <row r="41" customFormat="1" ht="15.75" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3820,7 +3826,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="15" spans="1:20">
+    <row r="42" customFormat="1" ht="15.75" spans="1:20">
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
@@ -3882,7 +3888,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="15" spans="1:20">
+    <row r="43" customFormat="1" ht="15.75" spans="1:20">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3924,7 +3930,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="15" spans="1:20">
+    <row r="44" customFormat="1" ht="15.75" spans="1:20">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -4002,7 +4008,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
     </row>
-    <row r="46" customFormat="1" ht="15" spans="1:20">
+    <row r="46" customFormat="1" ht="15.75" spans="1:20">
       <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
@@ -4064,7 +4070,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="15" spans="1:20">
+    <row r="47" customFormat="1" ht="15.75" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4106,7 +4112,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="15" spans="1:20">
+    <row r="48" customFormat="1" ht="15.75" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4138,7 +4144,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="15" spans="1:16">
+    <row r="49" s="2" customFormat="1" ht="15.75" spans="1:16">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -4188,7 +4194,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="15" spans="1:20">
+    <row r="50" customFormat="1" ht="15.75" spans="1:20">
       <c r="A50" s="5" t="s">
         <v>20</v>
       </c>
@@ -4250,7 +4256,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="15" spans="1:20">
+    <row r="51" customFormat="1" ht="15.75" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4292,7 +4298,7 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="15" spans="1:20">
+    <row r="52" customFormat="1" ht="15.75" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4334,7 +4340,7 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="15" spans="1:12">
+    <row r="53" customFormat="1" ht="15.75" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>20</v>
       </c>
@@ -4372,7 +4378,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="15" spans="1:20">
+    <row r="54" customFormat="1" ht="15.75" spans="1:20">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4394,7 +4400,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="22"/>
     </row>
-    <row r="55" customFormat="1" ht="15" spans="1:20">
+    <row r="55" customFormat="1" ht="15.75" spans="1:20">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4416,7 +4422,7 @@
       <c r="S55" s="22"/>
       <c r="T55" s="22"/>
     </row>
-    <row r="56" customFormat="1" ht="15" spans="1:20">
+    <row r="56" customFormat="1" ht="15.75" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4438,7 +4444,7 @@
       <c r="S56" s="22"/>
       <c r="T56" s="22"/>
     </row>
-    <row r="57" customFormat="1" ht="15" spans="1:20">
+    <row r="57" customFormat="1" ht="15.75" spans="1:20">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4460,7 +4466,7 @@
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
     </row>
-    <row r="58" customFormat="1" ht="15" spans="1:20">
+    <row r="58" customFormat="1" ht="15.75" spans="1:20">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4482,7 +4488,7 @@
       <c r="S58" s="27"/>
       <c r="T58" s="27"/>
     </row>
-    <row r="59" customFormat="1" ht="15" spans="1:20">
+    <row r="59" customFormat="1" ht="15.75" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4504,7 +4510,7 @@
       <c r="S59" s="27"/>
       <c r="T59" s="27"/>
     </row>
-    <row r="60" customFormat="1" ht="15" spans="1:20">
+    <row r="60" customFormat="1" ht="15.75" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="12090"/>
+    <workbookView windowWidth="25600" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="Doing" sheetId="1" r:id="rId1"/>
@@ -1189,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1269,9 +1269,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1593,21 +1590,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="5.58333333333333" customWidth="1"/>
-    <col min="3" max="3" width="11.1833333333333" customWidth="1"/>
+    <col min="1" max="2" width="5.58181818181818" customWidth="1"/>
+    <col min="3" max="3" width="11.1818181818182" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="20.8166666666667" customWidth="1"/>
+    <col min="5" max="5" width="20.8181818181818" customWidth="1"/>
     <col min="6" max="6" width="7.5" customWidth="1"/>
-    <col min="7" max="7" width="26.5416666666667" customWidth="1"/>
-    <col min="8" max="8" width="9.875" customWidth="1"/>
-    <col min="9" max="9" width="9.125" customWidth="1"/>
-    <col min="10" max="10" width="10.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="26.5454545454545" customWidth="1"/>
+    <col min="8" max="8" width="9.87272727272727" customWidth="1"/>
+    <col min="9" max="9" width="9.12727272727273" customWidth="1"/>
+    <col min="10" max="10" width="10.8363636363636" customWidth="1"/>
     <col min="11" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:20">
+    <row r="1" ht="15" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1669,7 +1666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15.75" spans="1:18">
+    <row r="2" customFormat="1" ht="15" spans="1:19">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1721,16 +1718,19 @@
       <c r="Q2" s="21">
         <v>46046</v>
       </c>
-      <c r="R2" s="30">
+      <c r="R2" s="22">
         <v>46116</v>
       </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15.75"/>
-    <row r="12" s="2" customFormat="1" ht="15.75"/>
-    <row r="13" s="2" customFormat="1" ht="15.75"/>
-    <row r="14" s="2" customFormat="1" ht="15.75"/>
-    <row r="15" s="2" customFormat="1" ht="15.75"/>
-    <row r="16" s="2" customFormat="1" ht="15.75" spans="1:9">
+      <c r="S2" s="22">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="15"/>
+    <row r="12" s="2" customFormat="1" ht="15"/>
+    <row r="13" s="2" customFormat="1" ht="15"/>
+    <row r="14" s="2" customFormat="1" ht="15"/>
+    <row r="15" s="2" customFormat="1" ht="15"/>
+    <row r="16" s="2" customFormat="1" ht="15" spans="1:9">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -1741,7 +1741,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="15.75" spans="1:9">
+    <row r="17" s="2" customFormat="1" ht="15" spans="1:9">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -1752,7 +1752,7 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" ht="18.75" spans="2:13">
+    <row r="18" ht="17.5" spans="2:13">
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
@@ -1768,7 +1768,7 @@
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" ht="18.75" spans="2:13">
+    <row r="19" ht="17.5" spans="2:13">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1782,7 +1782,7 @@
       <c r="L19" s="29"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" ht="18.75" spans="2:12">
+    <row r="20" ht="17.5" spans="2:12">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1794,7 +1794,7 @@
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" ht="18.75" spans="2:13">
+    <row r="21" ht="17.5" spans="2:13">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1808,7 +1808,7 @@
       <c r="L21" s="29"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" ht="18.75" spans="2:13">
+    <row r="22" ht="17.5" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1836,22 +1836,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="4.58333333333333" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="17.725" customWidth="1"/>
-    <col min="5" max="5" width="23.1833333333333" customWidth="1"/>
-    <col min="6" max="6" width="7.33333333333333" customWidth="1"/>
-    <col min="7" max="7" width="27.125" customWidth="1"/>
-    <col min="8" max="9" width="9.58333333333333" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="20" width="11.275" customWidth="1"/>
-    <col min="21" max="21" width="10.7583333333333" customWidth="1"/>
+    <col min="1" max="2" width="4.58181818181818" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="17.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="23.1818181818182" customWidth="1"/>
+    <col min="6" max="6" width="7.33636363636364" customWidth="1"/>
+    <col min="7" max="7" width="27.1272727272727" customWidth="1"/>
+    <col min="8" max="9" width="9.58181818181818" customWidth="1"/>
+    <col min="10" max="10" width="10.6272727272727" customWidth="1"/>
+    <col min="11" max="20" width="11.2727272727273" customWidth="1"/>
+    <col min="21" max="21" width="10.7545454545455" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:21">
+    <row r="1" ht="15" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15.75" spans="1:21">
+    <row r="2" customFormat="1" ht="15" spans="1:21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="15.75" spans="1:19">
+    <row r="3" customFormat="1" ht="15" spans="1:19">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>45304</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="15.75" spans="1:11">
+    <row r="4" customFormat="1" ht="15" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="15.75" spans="1:20">
+    <row r="5" customFormat="1" ht="15" spans="1:20">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" customFormat="1" ht="15.75" spans="1:20">
+    <row r="6" customFormat="1" ht="15" spans="1:20">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>45344</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="15.75" spans="1:20">
+    <row r="7" customFormat="1" ht="15" spans="1:20">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="15.75" spans="1:20">
+    <row r="9" customFormat="1" ht="15" spans="1:20">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>45263</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="15.75" spans="1:20">
+    <row r="10" customFormat="1" ht="15" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2388,7 +2388,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="15.75" spans="1:20">
+    <row r="11" customFormat="1" ht="15" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2430,7 +2430,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="15.75" spans="1:20">
+    <row r="12" customFormat="1" ht="15" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2454,7 +2454,7 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="1" ht="15.75" spans="1:20">
+    <row r="13" customFormat="1" ht="15" spans="1:20">
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="15.75" spans="1:20">
+    <row r="14" customFormat="1" ht="15" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2540,7 +2540,7 @@
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" customFormat="1" ht="15.75" spans="1:20">
+    <row r="15" customFormat="1" ht="15" spans="1:20">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -2596,7 +2596,7 @@
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" customFormat="1" ht="15.75" spans="1:20">
+    <row r="16" customFormat="1" ht="15" spans="1:20">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="15.75" spans="1:20">
+    <row r="17" customFormat="1" ht="15" spans="1:20">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="15.75" spans="1:20">
+    <row r="18" customFormat="1" ht="15" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2752,7 +2752,7 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
     </row>
-    <row r="19" customFormat="1" ht="15.75" spans="1:20">
+    <row r="19" customFormat="1" ht="15" spans="1:20">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="15.75" spans="1:20">
+    <row r="20" customFormat="1" ht="15" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2846,7 +2846,7 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
     </row>
-    <row r="21" customFormat="1" ht="15.75" spans="1:20">
+    <row r="21" customFormat="1" ht="15" spans="1:20">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="15.75" spans="1:20">
+    <row r="22" customFormat="1" ht="15" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2950,7 +2950,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="15.75" spans="1:20">
+    <row r="23" customFormat="1" ht="15" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2982,7 +2982,7 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="15.75" spans="1:20">
+    <row r="24" customFormat="1" ht="15" spans="1:20">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="15.75" spans="1:20">
+    <row r="25" customFormat="1" ht="15" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3086,7 +3086,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:20">
+    <row r="26" s="1" customFormat="1" ht="15" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3124,7 +3124,7 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
     </row>
-    <row r="27" customFormat="1" ht="15.75" spans="1:20">
+    <row r="27" customFormat="1" ht="15" spans="1:20">
       <c r="A27" s="6" t="s">
         <v>103</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="S27" s="25"/>
       <c r="T27" s="25"/>
     </row>
-    <row r="28" customFormat="1" ht="15.75" spans="1:20">
+    <row r="28" customFormat="1" ht="15" spans="1:20">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -3222,7 +3222,7 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
     </row>
-    <row r="29" customFormat="1" ht="15.75" spans="1:18">
+    <row r="29" customFormat="1" ht="15" spans="1:18">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -3264,7 +3264,7 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
     </row>
-    <row r="30" customFormat="1" ht="15.75" spans="1:20">
+    <row r="30" customFormat="1" ht="15" spans="1:20">
       <c r="A30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" customFormat="1" ht="15.75" spans="1:20">
+    <row r="31" customFormat="1" ht="15" spans="1:20">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="15.75" spans="1:20">
+    <row r="32" customFormat="1" ht="15" spans="1:20">
       <c r="A32" s="5" t="s">
         <v>20</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="15.75" spans="1:20">
+    <row r="33" customFormat="1" ht="15" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3470,7 +3470,7 @@
       <c r="S33" s="22"/>
       <c r="T33" s="22"/>
     </row>
-    <row r="34" customFormat="1" ht="15.75" spans="1:20">
+    <row r="34" customFormat="1" ht="15" spans="1:20">
       <c r="A34" s="6" t="s">
         <v>20</v>
       </c>
@@ -3526,7 +3526,7 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
     </row>
-    <row r="35" customFormat="1" ht="15.75" spans="1:20">
+    <row r="35" customFormat="1" ht="15" spans="1:20">
       <c r="A35" s="5" t="s">
         <v>20</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="15.75" spans="1:20">
+    <row r="36" customFormat="1" ht="15" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3630,7 +3630,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="15.75" spans="1:20">
+    <row r="37" customFormat="1" ht="15" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3672,7 +3672,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="15.75" spans="1:20">
+    <row r="38" customFormat="1" ht="15" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3701,7 +3701,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" customFormat="1" ht="15.75" spans="1:20">
+    <row r="39" customFormat="1" ht="15" spans="1:20">
       <c r="A39" s="5" t="s">
         <v>20</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>45592</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="15.75" spans="1:20">
+    <row r="40" customFormat="1" ht="15" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3805,7 +3805,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="15.75" spans="1:13">
+    <row r="41" customFormat="1" ht="15" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3826,7 +3826,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="15.75" spans="1:20">
+    <row r="42" customFormat="1" ht="15" spans="1:20">
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="15.75" spans="1:20">
+    <row r="43" customFormat="1" ht="15" spans="1:20">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3930,7 +3930,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="15.75" spans="1:20">
+    <row r="44" customFormat="1" ht="15" spans="1:20">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -4008,7 +4008,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
     </row>
-    <row r="46" customFormat="1" ht="15.75" spans="1:20">
+    <row r="46" customFormat="1" ht="15" spans="1:20">
       <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="15.75" spans="1:20">
+    <row r="47" customFormat="1" ht="15" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4112,7 +4112,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="15.75" spans="1:20">
+    <row r="48" customFormat="1" ht="15" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4144,7 +4144,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="15.75" spans="1:16">
+    <row r="49" s="2" customFormat="1" ht="15" spans="1:16">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="15.75" spans="1:20">
+    <row r="50" customFormat="1" ht="15" spans="1:20">
       <c r="A50" s="5" t="s">
         <v>20</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="15.75" spans="1:20">
+    <row r="51" customFormat="1" ht="15" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4298,7 +4298,7 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="15.75" spans="1:20">
+    <row r="52" customFormat="1" ht="15" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4340,7 +4340,7 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="15.75" spans="1:12">
+    <row r="53" customFormat="1" ht="15" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>20</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="15.75" spans="1:20">
+    <row r="54" customFormat="1" ht="15" spans="1:20">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4400,7 +4400,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="22"/>
     </row>
-    <row r="55" customFormat="1" ht="15.75" spans="1:20">
+    <row r="55" customFormat="1" ht="15" spans="1:20">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4422,7 +4422,7 @@
       <c r="S55" s="22"/>
       <c r="T55" s="22"/>
     </row>
-    <row r="56" customFormat="1" ht="15.75" spans="1:20">
+    <row r="56" customFormat="1" ht="15" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4444,7 +4444,7 @@
       <c r="S56" s="22"/>
       <c r="T56" s="22"/>
     </row>
-    <row r="57" customFormat="1" ht="15.75" spans="1:20">
+    <row r="57" customFormat="1" ht="15" spans="1:20">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4466,7 +4466,7 @@
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
     </row>
-    <row r="58" customFormat="1" ht="15.75" spans="1:20">
+    <row r="58" customFormat="1" ht="15" spans="1:20">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4488,7 +4488,7 @@
       <c r="S58" s="27"/>
       <c r="T58" s="27"/>
     </row>
-    <row r="59" customFormat="1" ht="15.75" spans="1:20">
+    <row r="59" customFormat="1" ht="15" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4510,7 +4510,7 @@
       <c r="S59" s="27"/>
       <c r="T59" s="27"/>
     </row>
-    <row r="60" customFormat="1" ht="15.75" spans="1:20">
+    <row r="60" customFormat="1" ht="15" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12330"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Doing" sheetId="1" r:id="rId1"/>
@@ -1590,21 +1590,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="5.58181818181818" customWidth="1"/>
-    <col min="3" max="3" width="11.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="20.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="7.5" customWidth="1"/>
-    <col min="7" max="7" width="26.5454545454545" customWidth="1"/>
-    <col min="8" max="8" width="9.87272727272727" customWidth="1"/>
-    <col min="9" max="9" width="9.12727272727273" customWidth="1"/>
-    <col min="10" max="10" width="10.8363636363636" customWidth="1"/>
+    <col min="1" max="2" width="5.375" customWidth="1"/>
+    <col min="3" max="3" width="11.1833333333333" customWidth="1"/>
+    <col min="4" max="4" width="7.875" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="6.875" customWidth="1"/>
+    <col min="7" max="7" width="24.25" customWidth="1"/>
+    <col min="8" max="8" width="6.125" customWidth="1"/>
+    <col min="9" max="9" width="9.125" customWidth="1"/>
+    <col min="10" max="10" width="10.8333333333333" customWidth="1"/>
     <col min="11" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15.75" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15" spans="1:19">
+    <row r="2" customFormat="1" ht="15.75" spans="1:19">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1718,19 +1718,19 @@
       <c r="Q2" s="21">
         <v>46046</v>
       </c>
-      <c r="R2" s="22">
+      <c r="R2" s="21">
         <v>46116</v>
       </c>
-      <c r="S2" s="22">
+      <c r="S2" s="21">
         <v>46123</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="15"/>
-    <row r="12" s="2" customFormat="1" ht="15"/>
-    <row r="13" s="2" customFormat="1" ht="15"/>
-    <row r="14" s="2" customFormat="1" ht="15"/>
-    <row r="15" s="2" customFormat="1" ht="15"/>
-    <row r="16" s="2" customFormat="1" ht="15" spans="1:9">
+    <row r="11" s="2" customFormat="1" ht="15.75"/>
+    <row r="12" s="2" customFormat="1" ht="15.75"/>
+    <row r="13" s="2" customFormat="1" ht="15.75"/>
+    <row r="14" s="2" customFormat="1" ht="15.75"/>
+    <row r="15" s="2" customFormat="1" ht="15.75"/>
+    <row r="16" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -1741,7 +1741,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="15" spans="1:9">
+    <row r="17" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -1752,7 +1752,7 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" ht="17.5" spans="2:13">
+    <row r="18" ht="18.75" spans="2:13">
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
@@ -1768,7 +1768,7 @@
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" ht="17.5" spans="2:13">
+    <row r="19" ht="18.75" spans="2:13">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1782,7 +1782,7 @@
       <c r="L19" s="29"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" ht="17.5" spans="2:12">
+    <row r="20" ht="18.75" spans="2:12">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1794,7 +1794,7 @@
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" ht="17.5" spans="2:13">
+    <row r="21" ht="18.75" spans="2:13">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1808,7 +1808,7 @@
       <c r="L21" s="29"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" ht="17.5" spans="2:13">
+    <row r="22" ht="18.75" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1836,22 +1836,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="4.58181818181818" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="17.7272727272727" customWidth="1"/>
-    <col min="5" max="5" width="23.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="7.33636363636364" customWidth="1"/>
-    <col min="7" max="7" width="27.1272727272727" customWidth="1"/>
-    <col min="8" max="9" width="9.58181818181818" customWidth="1"/>
-    <col min="10" max="10" width="10.6272727272727" customWidth="1"/>
-    <col min="11" max="20" width="11.2727272727273" customWidth="1"/>
-    <col min="21" max="21" width="10.7545454545455" customWidth="1"/>
+    <col min="1" max="2" width="4.58333333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="17.725" customWidth="1"/>
+    <col min="5" max="5" width="23.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.33333333333333" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
+    <col min="8" max="9" width="9.58333333333333" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="20" width="11.275" customWidth="1"/>
+    <col min="21" max="21" width="10.7583333333333" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:21">
+    <row r="1" ht="15.75" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15" spans="1:21">
+    <row r="2" customFormat="1" ht="15.75" spans="1:21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="15" spans="1:19">
+    <row r="3" customFormat="1" ht="15.75" spans="1:19">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>45304</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="15" spans="1:11">
+    <row r="4" customFormat="1" ht="15.75" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="15" spans="1:20">
+    <row r="5" customFormat="1" ht="15.75" spans="1:20">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" customFormat="1" ht="15" spans="1:20">
+    <row r="6" customFormat="1" ht="15.75" spans="1:20">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>45344</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="15" spans="1:20">
+    <row r="7" customFormat="1" ht="15.75" spans="1:20">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -2284,7 +2284,7 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="15" spans="1:20">
+    <row r="9" customFormat="1" ht="15.75" spans="1:20">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>45263</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="15" spans="1:20">
+    <row r="10" customFormat="1" ht="15.75" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2388,7 +2388,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="15" spans="1:20">
+    <row r="11" customFormat="1" ht="15.75" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2430,7 +2430,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="15" spans="1:20">
+    <row r="12" customFormat="1" ht="15.75" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2454,7 +2454,7 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="1" ht="15" spans="1:20">
+    <row r="13" customFormat="1" ht="15.75" spans="1:20">
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="15" spans="1:20">
+    <row r="14" customFormat="1" ht="15.75" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2540,7 +2540,7 @@
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" customFormat="1" ht="15" spans="1:20">
+    <row r="15" customFormat="1" ht="15.75" spans="1:20">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -2596,7 +2596,7 @@
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" customFormat="1" ht="15" spans="1:20">
+    <row r="16" customFormat="1" ht="15.75" spans="1:20">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="15" spans="1:20">
+    <row r="17" customFormat="1" ht="15.75" spans="1:20">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="15" spans="1:20">
+    <row r="18" customFormat="1" ht="15.75" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2752,7 +2752,7 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
     </row>
-    <row r="19" customFormat="1" ht="15" spans="1:20">
+    <row r="19" customFormat="1" ht="15.75" spans="1:20">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="15" spans="1:20">
+    <row r="20" customFormat="1" ht="15.75" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2846,7 +2846,7 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
     </row>
-    <row r="21" customFormat="1" ht="15" spans="1:20">
+    <row r="21" customFormat="1" ht="15.75" spans="1:20">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="15" spans="1:20">
+    <row r="22" customFormat="1" ht="15.75" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2950,7 +2950,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="15" spans="1:20">
+    <row r="23" customFormat="1" ht="15.75" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2982,7 +2982,7 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="15" spans="1:20">
+    <row r="24" customFormat="1" ht="15.75" spans="1:20">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="15" spans="1:20">
+    <row r="25" customFormat="1" ht="15.75" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3086,7 +3086,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="15" spans="1:20">
+    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3124,7 +3124,7 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
     </row>
-    <row r="27" customFormat="1" ht="15" spans="1:20">
+    <row r="27" customFormat="1" ht="15.75" spans="1:20">
       <c r="A27" s="6" t="s">
         <v>103</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="S27" s="25"/>
       <c r="T27" s="25"/>
     </row>
-    <row r="28" customFormat="1" ht="15" spans="1:20">
+    <row r="28" customFormat="1" ht="15.75" spans="1:20">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -3222,7 +3222,7 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
     </row>
-    <row r="29" customFormat="1" ht="15" spans="1:18">
+    <row r="29" customFormat="1" ht="15.75" spans="1:18">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -3264,7 +3264,7 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
     </row>
-    <row r="30" customFormat="1" ht="15" spans="1:20">
+    <row r="30" customFormat="1" ht="15.75" spans="1:20">
       <c r="A30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" customFormat="1" ht="15" spans="1:20">
+    <row r="31" customFormat="1" ht="15.75" spans="1:20">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="15" spans="1:20">
+    <row r="32" customFormat="1" ht="15.75" spans="1:20">
       <c r="A32" s="5" t="s">
         <v>20</v>
       </c>
@@ -3442,7 +3442,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="15" spans="1:20">
+    <row r="33" customFormat="1" ht="15.75" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3470,7 +3470,7 @@
       <c r="S33" s="22"/>
       <c r="T33" s="22"/>
     </row>
-    <row r="34" customFormat="1" ht="15" spans="1:20">
+    <row r="34" customFormat="1" ht="15.75" spans="1:20">
       <c r="A34" s="6" t="s">
         <v>20</v>
       </c>
@@ -3526,7 +3526,7 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
     </row>
-    <row r="35" customFormat="1" ht="15" spans="1:20">
+    <row r="35" customFormat="1" ht="15.75" spans="1:20">
       <c r="A35" s="5" t="s">
         <v>20</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="15" spans="1:20">
+    <row r="36" customFormat="1" ht="15.75" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3630,7 +3630,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="15" spans="1:20">
+    <row r="37" customFormat="1" ht="15.75" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3672,7 +3672,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="15" spans="1:20">
+    <row r="38" customFormat="1" ht="15.75" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3701,7 +3701,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" customFormat="1" ht="15" spans="1:20">
+    <row r="39" customFormat="1" ht="15.75" spans="1:20">
       <c r="A39" s="5" t="s">
         <v>20</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>45592</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="15" spans="1:20">
+    <row r="40" customFormat="1" ht="15.75" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3805,7 +3805,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="15" spans="1:13">
+    <row r="41" customFormat="1" ht="15.75" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3826,7 +3826,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="15" spans="1:20">
+    <row r="42" customFormat="1" ht="15.75" spans="1:20">
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="15" spans="1:20">
+    <row r="43" customFormat="1" ht="15.75" spans="1:20">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3930,7 +3930,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="15" spans="1:20">
+    <row r="44" customFormat="1" ht="15.75" spans="1:20">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -4008,7 +4008,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
     </row>
-    <row r="46" customFormat="1" ht="15" spans="1:20">
+    <row r="46" customFormat="1" ht="15.75" spans="1:20">
       <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="15" spans="1:20">
+    <row r="47" customFormat="1" ht="15.75" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4112,7 +4112,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="15" spans="1:20">
+    <row r="48" customFormat="1" ht="15.75" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4144,7 +4144,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="15" spans="1:16">
+    <row r="49" s="2" customFormat="1" ht="15.75" spans="1:16">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="15" spans="1:20">
+    <row r="50" customFormat="1" ht="15.75" spans="1:20">
       <c r="A50" s="5" t="s">
         <v>20</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="15" spans="1:20">
+    <row r="51" customFormat="1" ht="15.75" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4298,7 +4298,7 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="15" spans="1:20">
+    <row r="52" customFormat="1" ht="15.75" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4340,7 +4340,7 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="15" spans="1:12">
+    <row r="53" customFormat="1" ht="15.75" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>20</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="15" spans="1:20">
+    <row r="54" customFormat="1" ht="15.75" spans="1:20">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4400,7 +4400,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="22"/>
     </row>
-    <row r="55" customFormat="1" ht="15" spans="1:20">
+    <row r="55" customFormat="1" ht="15.75" spans="1:20">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4422,7 +4422,7 @@
       <c r="S55" s="22"/>
       <c r="T55" s="22"/>
     </row>
-    <row r="56" customFormat="1" ht="15" spans="1:20">
+    <row r="56" customFormat="1" ht="15.75" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4444,7 +4444,7 @@
       <c r="S56" s="22"/>
       <c r="T56" s="22"/>
     </row>
-    <row r="57" customFormat="1" ht="15" spans="1:20">
+    <row r="57" customFormat="1" ht="15.75" spans="1:20">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4466,7 +4466,7 @@
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
     </row>
-    <row r="58" customFormat="1" ht="15" spans="1:20">
+    <row r="58" customFormat="1" ht="15.75" spans="1:20">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4488,7 +4488,7 @@
       <c r="S58" s="27"/>
       <c r="T58" s="27"/>
     </row>
-    <row r="59" customFormat="1" ht="15" spans="1:20">
+    <row r="59" customFormat="1" ht="15.75" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4510,7 +4510,7 @@
       <c r="S59" s="27"/>
       <c r="T59" s="27"/>
     </row>
-    <row r="60" customFormat="1" ht="15" spans="1:20">
+    <row r="60" customFormat="1" ht="15.75" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -1189,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1269,6 +1269,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1666,7 +1669,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15.75" spans="1:19">
+    <row r="2" customFormat="1" ht="15.75" spans="1:20">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1723,6 +1726,9 @@
       </c>
       <c r="S2" s="21">
         <v>46123</v>
+      </c>
+      <c r="T2" s="30">
+        <v>46131</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="15.75"/>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -89,7 +89,7 @@
     <t>240/2h</t>
   </si>
   <si>
-    <t>周六12：30-14：30</t>
+    <t>周日10：00-12：00</t>
   </si>
   <si>
     <t>安芯宇</t>
@@ -1189,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1269,9 +1269,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1691,10 +1688,10 @@
       <c r="G2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J2" s="21" t="s">
@@ -1727,8 +1724,23 @@
       <c r="S2" s="21">
         <v>46123</v>
       </c>
-      <c r="T2" s="30">
+      <c r="T2" s="22">
         <v>46131</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" spans="1:11">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22">
+        <v>46138</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="15.75"/>
@@ -1829,7 +1841,17 @@
       <c r="M22" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="11">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
     <mergeCell ref="B18:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -1724,7 +1724,7 @@
       <c r="S2" s="21">
         <v>46123</v>
       </c>
-      <c r="T2" s="22">
+      <c r="T2" s="21">
         <v>46131</v>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="21"/>
-      <c r="K3" s="22">
+      <c r="K3" s="21">
         <v>46138</v>
       </c>
     </row>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="25600" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="Doing" sheetId="1" r:id="rId1"/>
@@ -1590,21 +1590,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="5.375" customWidth="1"/>
-    <col min="3" max="3" width="11.1833333333333" customWidth="1"/>
-    <col min="4" max="4" width="7.875" customWidth="1"/>
+    <col min="1" max="2" width="5.37272727272727" customWidth="1"/>
+    <col min="3" max="3" width="11.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="7.87272727272727" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="6.875" customWidth="1"/>
-    <col min="7" max="7" width="24.25" customWidth="1"/>
-    <col min="8" max="8" width="6.125" customWidth="1"/>
-    <col min="9" max="9" width="9.125" customWidth="1"/>
-    <col min="10" max="10" width="10.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="6.87272727272727" customWidth="1"/>
+    <col min="7" max="7" width="24.2545454545455" customWidth="1"/>
+    <col min="8" max="8" width="6.12727272727273" customWidth="1"/>
+    <col min="9" max="9" width="9.12727272727273" customWidth="1"/>
+    <col min="10" max="10" width="10.8363636363636" customWidth="1"/>
     <col min="11" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:20">
+    <row r="1" ht="15" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15.75" spans="1:20">
+    <row r="2" customFormat="1" ht="15" spans="1:20">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1724,11 +1724,11 @@
       <c r="S2" s="21">
         <v>46123</v>
       </c>
-      <c r="T2" s="22">
+      <c r="T2" s="21">
         <v>46131</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:11">
+    <row r="3" ht="15" spans="1:12">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1739,16 +1739,19 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="21"/>
-      <c r="K3" s="22">
+      <c r="K3" s="21">
         <v>46138</v>
       </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15.75"/>
-    <row r="12" s="2" customFormat="1" ht="15.75"/>
-    <row r="13" s="2" customFormat="1" ht="15.75"/>
-    <row r="14" s="2" customFormat="1" ht="15.75"/>
-    <row r="15" s="2" customFormat="1" ht="15.75"/>
-    <row r="16" s="2" customFormat="1" ht="15.75" spans="1:9">
+      <c r="L3" s="22">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="15"/>
+    <row r="12" s="2" customFormat="1" ht="15"/>
+    <row r="13" s="2" customFormat="1" ht="15"/>
+    <row r="14" s="2" customFormat="1" ht="15"/>
+    <row r="15" s="2" customFormat="1" ht="15"/>
+    <row r="16" s="2" customFormat="1" ht="15" spans="1:9">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -1759,7 +1762,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="15.75" spans="1:9">
+    <row r="17" s="2" customFormat="1" ht="15" spans="1:9">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -1770,7 +1773,7 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" ht="18.75" spans="2:13">
+    <row r="18" ht="17.5" spans="2:13">
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
@@ -1786,7 +1789,7 @@
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" ht="18.75" spans="2:13">
+    <row r="19" ht="17.5" spans="2:13">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1800,7 +1803,7 @@
       <c r="L19" s="29"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" ht="18.75" spans="2:12">
+    <row r="20" ht="17.5" spans="2:12">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1812,7 +1815,7 @@
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" ht="18.75" spans="2:13">
+    <row r="21" ht="17.5" spans="2:13">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1826,7 +1829,7 @@
       <c r="L21" s="29"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" ht="18.75" spans="2:13">
+    <row r="22" ht="17.5" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1864,22 +1867,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="4.58333333333333" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="17.725" customWidth="1"/>
-    <col min="5" max="5" width="23.1833333333333" customWidth="1"/>
-    <col min="6" max="6" width="7.33333333333333" customWidth="1"/>
-    <col min="7" max="7" width="27.125" customWidth="1"/>
-    <col min="8" max="9" width="9.58333333333333" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="20" width="11.275" customWidth="1"/>
-    <col min="21" max="21" width="10.7583333333333" customWidth="1"/>
+    <col min="1" max="2" width="4.58181818181818" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="17.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="23.1818181818182" customWidth="1"/>
+    <col min="6" max="6" width="7.33636363636364" customWidth="1"/>
+    <col min="7" max="7" width="27.1272727272727" customWidth="1"/>
+    <col min="8" max="9" width="9.58181818181818" customWidth="1"/>
+    <col min="10" max="10" width="10.6272727272727" customWidth="1"/>
+    <col min="11" max="20" width="11.2727272727273" customWidth="1"/>
+    <col min="21" max="21" width="10.7545454545455" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:21">
+    <row r="1" ht="15" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1944,7 +1947,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15.75" spans="1:21">
+    <row r="2" customFormat="1" ht="15" spans="1:21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -2009,7 +2012,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="15.75" spans="1:19">
+    <row r="3" customFormat="1" ht="15" spans="1:19">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -2068,7 +2071,7 @@
         <v>45304</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="15.75" spans="1:11">
+    <row r="4" customFormat="1" ht="15" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -2103,7 +2106,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="15.75" spans="1:20">
+    <row r="5" customFormat="1" ht="15" spans="1:20">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -2163,7 +2166,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" customFormat="1" ht="15.75" spans="1:20">
+    <row r="6" customFormat="1" ht="15" spans="1:20">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -2225,7 +2228,7 @@
         <v>45344</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="15.75" spans="1:20">
+    <row r="7" customFormat="1" ht="15" spans="1:20">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -2312,7 +2315,7 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="15.75" spans="1:20">
+    <row r="9" customFormat="1" ht="15" spans="1:20">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>45263</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="15.75" spans="1:20">
+    <row r="10" customFormat="1" ht="15" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2416,7 +2419,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="15.75" spans="1:20">
+    <row r="11" customFormat="1" ht="15" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2458,7 +2461,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="15.75" spans="1:20">
+    <row r="12" customFormat="1" ht="15" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2482,7 +2485,7 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="1" ht="15.75" spans="1:20">
+    <row r="13" customFormat="1" ht="15" spans="1:20">
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
@@ -2544,7 +2547,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="15.75" spans="1:20">
+    <row r="14" customFormat="1" ht="15" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2568,7 +2571,7 @@
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" customFormat="1" ht="15.75" spans="1:20">
+    <row r="15" customFormat="1" ht="15" spans="1:20">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -2624,7 +2627,7 @@
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" customFormat="1" ht="15.75" spans="1:20">
+    <row r="16" customFormat="1" ht="15" spans="1:20">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -2686,7 +2689,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="15.75" spans="1:20">
+    <row r="17" customFormat="1" ht="15" spans="1:20">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -2748,7 +2751,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="15.75" spans="1:20">
+    <row r="18" customFormat="1" ht="15" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2780,7 +2783,7 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
     </row>
-    <row r="19" customFormat="1" ht="15.75" spans="1:20">
+    <row r="19" customFormat="1" ht="15" spans="1:20">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -2842,7 +2845,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="15.75" spans="1:20">
+    <row r="20" customFormat="1" ht="15" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2874,7 +2877,7 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
     </row>
-    <row r="21" customFormat="1" ht="15.75" spans="1:20">
+    <row r="21" customFormat="1" ht="15" spans="1:20">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -2936,7 +2939,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="15.75" spans="1:20">
+    <row r="22" customFormat="1" ht="15" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2978,7 +2981,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="15.75" spans="1:20">
+    <row r="23" customFormat="1" ht="15" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3010,7 +3013,7 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="15.75" spans="1:20">
+    <row r="24" customFormat="1" ht="15" spans="1:20">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
@@ -3072,7 +3075,7 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="15.75" spans="1:20">
+    <row r="25" customFormat="1" ht="15" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3114,7 +3117,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:20">
+    <row r="26" s="1" customFormat="1" ht="15" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3152,7 +3155,7 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
     </row>
-    <row r="27" customFormat="1" ht="15.75" spans="1:20">
+    <row r="27" customFormat="1" ht="15" spans="1:20">
       <c r="A27" s="6" t="s">
         <v>103</v>
       </c>
@@ -3196,7 +3199,7 @@
       <c r="S27" s="25"/>
       <c r="T27" s="25"/>
     </row>
-    <row r="28" customFormat="1" ht="15.75" spans="1:20">
+    <row r="28" customFormat="1" ht="15" spans="1:20">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -3250,7 +3253,7 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
     </row>
-    <row r="29" customFormat="1" ht="15.75" spans="1:18">
+    <row r="29" customFormat="1" ht="15" spans="1:18">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -3292,7 +3295,7 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
     </row>
-    <row r="30" customFormat="1" ht="15.75" spans="1:20">
+    <row r="30" customFormat="1" ht="15" spans="1:20">
       <c r="A30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3346,7 +3349,7 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" customFormat="1" ht="15.75" spans="1:20">
+    <row r="31" customFormat="1" ht="15" spans="1:20">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="15.75" spans="1:20">
+    <row r="32" customFormat="1" ht="15" spans="1:20">
       <c r="A32" s="5" t="s">
         <v>20</v>
       </c>
@@ -3470,7 +3473,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="15.75" spans="1:20">
+    <row r="33" customFormat="1" ht="15" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3498,7 +3501,7 @@
       <c r="S33" s="22"/>
       <c r="T33" s="22"/>
     </row>
-    <row r="34" customFormat="1" ht="15.75" spans="1:20">
+    <row r="34" customFormat="1" ht="15" spans="1:20">
       <c r="A34" s="6" t="s">
         <v>20</v>
       </c>
@@ -3554,7 +3557,7 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
     </row>
-    <row r="35" customFormat="1" ht="15.75" spans="1:20">
+    <row r="35" customFormat="1" ht="15" spans="1:20">
       <c r="A35" s="5" t="s">
         <v>20</v>
       </c>
@@ -3616,7 +3619,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="15.75" spans="1:20">
+    <row r="36" customFormat="1" ht="15" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3658,7 +3661,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="15.75" spans="1:20">
+    <row r="37" customFormat="1" ht="15" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3700,7 +3703,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="15.75" spans="1:20">
+    <row r="38" customFormat="1" ht="15" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3729,7 +3732,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" customFormat="1" ht="15.75" spans="1:20">
+    <row r="39" customFormat="1" ht="15" spans="1:20">
       <c r="A39" s="5" t="s">
         <v>20</v>
       </c>
@@ -3791,7 +3794,7 @@
         <v>45592</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="15.75" spans="1:20">
+    <row r="40" customFormat="1" ht="15" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3833,7 +3836,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="15.75" spans="1:13">
+    <row r="41" customFormat="1" ht="15" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3854,7 +3857,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="15.75" spans="1:20">
+    <row r="42" customFormat="1" ht="15" spans="1:20">
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
@@ -3916,7 +3919,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="15.75" spans="1:20">
+    <row r="43" customFormat="1" ht="15" spans="1:20">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3958,7 +3961,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="15.75" spans="1:20">
+    <row r="44" customFormat="1" ht="15" spans="1:20">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -4036,7 +4039,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
     </row>
-    <row r="46" customFormat="1" ht="15.75" spans="1:20">
+    <row r="46" customFormat="1" ht="15" spans="1:20">
       <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
@@ -4098,7 +4101,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="15.75" spans="1:20">
+    <row r="47" customFormat="1" ht="15" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4140,7 +4143,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="15.75" spans="1:20">
+    <row r="48" customFormat="1" ht="15" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4172,7 +4175,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="15.75" spans="1:16">
+    <row r="49" s="2" customFormat="1" ht="15" spans="1:16">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -4222,7 +4225,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="15.75" spans="1:20">
+    <row r="50" customFormat="1" ht="15" spans="1:20">
       <c r="A50" s="5" t="s">
         <v>20</v>
       </c>
@@ -4284,7 +4287,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="15.75" spans="1:20">
+    <row r="51" customFormat="1" ht="15" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4326,7 +4329,7 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="15.75" spans="1:20">
+    <row r="52" customFormat="1" ht="15" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4368,7 +4371,7 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="15.75" spans="1:12">
+    <row r="53" customFormat="1" ht="15" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>20</v>
       </c>
@@ -4406,7 +4409,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="15.75" spans="1:20">
+    <row r="54" customFormat="1" ht="15" spans="1:20">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4428,7 +4431,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="22"/>
     </row>
-    <row r="55" customFormat="1" ht="15.75" spans="1:20">
+    <row r="55" customFormat="1" ht="15" spans="1:20">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4450,7 +4453,7 @@
       <c r="S55" s="22"/>
       <c r="T55" s="22"/>
     </row>
-    <row r="56" customFormat="1" ht="15.75" spans="1:20">
+    <row r="56" customFormat="1" ht="15" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4472,7 +4475,7 @@
       <c r="S56" s="22"/>
       <c r="T56" s="22"/>
     </row>
-    <row r="57" customFormat="1" ht="15.75" spans="1:20">
+    <row r="57" customFormat="1" ht="15" spans="1:20">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4494,7 +4497,7 @@
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
     </row>
-    <row r="58" customFormat="1" ht="15.75" spans="1:20">
+    <row r="58" customFormat="1" ht="15" spans="1:20">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4516,7 +4519,7 @@
       <c r="S58" s="27"/>
       <c r="T58" s="27"/>
     </row>
-    <row r="59" customFormat="1" ht="15.75" spans="1:20">
+    <row r="59" customFormat="1" ht="15" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4538,7 +4541,7 @@
       <c r="S59" s="27"/>
       <c r="T59" s="27"/>
     </row>
-    <row r="60" customFormat="1" ht="15.75" spans="1:20">
+    <row r="60" customFormat="1" ht="15" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12330"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="Doing" sheetId="1" r:id="rId1"/>
@@ -1590,21 +1590,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="5.37272727272727" customWidth="1"/>
-    <col min="3" max="3" width="11.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="7.87272727272727" customWidth="1"/>
+    <col min="1" max="2" width="5.375" customWidth="1"/>
+    <col min="3" max="3" width="11.1833333333333" customWidth="1"/>
+    <col min="4" max="4" width="7.875" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="6.87272727272727" customWidth="1"/>
-    <col min="7" max="7" width="24.2545454545455" customWidth="1"/>
-    <col min="8" max="8" width="6.12727272727273" customWidth="1"/>
-    <col min="9" max="9" width="9.12727272727273" customWidth="1"/>
-    <col min="10" max="10" width="10.8363636363636" customWidth="1"/>
+    <col min="6" max="6" width="6.875" customWidth="1"/>
+    <col min="7" max="7" width="24.2583333333333" customWidth="1"/>
+    <col min="8" max="8" width="6.125" customWidth="1"/>
+    <col min="9" max="9" width="9.125" customWidth="1"/>
+    <col min="10" max="10" width="10.8333333333333" customWidth="1"/>
     <col min="11" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15.75" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15" spans="1:20">
+    <row r="2" customFormat="1" ht="15.75" spans="1:20">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="3" ht="15" spans="1:12">
+    <row r="3" ht="15.75" spans="1:13">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1745,13 +1745,16 @@
       <c r="L3" s="22">
         <v>46143</v>
       </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15"/>
-    <row r="12" s="2" customFormat="1" ht="15"/>
-    <row r="13" s="2" customFormat="1" ht="15"/>
-    <row r="14" s="2" customFormat="1" ht="15"/>
-    <row r="15" s="2" customFormat="1" ht="15"/>
-    <row r="16" s="2" customFormat="1" ht="15" spans="1:9">
+      <c r="M3" s="22">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="15.75"/>
+    <row r="12" s="2" customFormat="1" ht="15.75"/>
+    <row r="13" s="2" customFormat="1" ht="15.75"/>
+    <row r="14" s="2" customFormat="1" ht="15.75"/>
+    <row r="15" s="2" customFormat="1" ht="15.75"/>
+    <row r="16" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -1762,7 +1765,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="15" spans="1:9">
+    <row r="17" s="2" customFormat="1" ht="15.75" spans="1:9">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -1773,7 +1776,7 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" ht="17.5" spans="2:13">
+    <row r="18" ht="18.75" spans="2:13">
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
@@ -1789,7 +1792,7 @@
       <c r="L18" s="29"/>
       <c r="M18" s="29"/>
     </row>
-    <row r="19" ht="17.5" spans="2:13">
+    <row r="19" ht="18.75" spans="2:13">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1803,7 +1806,7 @@
       <c r="L19" s="29"/>
       <c r="M19" s="29"/>
     </row>
-    <row r="20" ht="17.5" spans="2:12">
+    <row r="20" ht="18.75" spans="2:12">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1815,7 +1818,7 @@
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
     </row>
-    <row r="21" ht="17.5" spans="2:13">
+    <row r="21" ht="18.75" spans="2:13">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1829,7 +1832,7 @@
       <c r="L21" s="29"/>
       <c r="M21" s="29"/>
     </row>
-    <row r="22" ht="17.5" spans="2:13">
+    <row r="22" ht="18.75" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1867,22 +1870,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="4.58181818181818" customWidth="1"/>
-    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
-    <col min="4" max="4" width="17.7272727272727" customWidth="1"/>
-    <col min="5" max="5" width="23.1818181818182" customWidth="1"/>
-    <col min="6" max="6" width="7.33636363636364" customWidth="1"/>
-    <col min="7" max="7" width="27.1272727272727" customWidth="1"/>
-    <col min="8" max="9" width="9.58181818181818" customWidth="1"/>
-    <col min="10" max="10" width="10.6272727272727" customWidth="1"/>
-    <col min="11" max="20" width="11.2727272727273" customWidth="1"/>
-    <col min="21" max="21" width="10.7545454545455" customWidth="1"/>
+    <col min="1" max="2" width="4.58333333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="17.725" customWidth="1"/>
+    <col min="5" max="5" width="23.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="7.33333333333333" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
+    <col min="8" max="9" width="9.58333333333333" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="20" width="11.275" customWidth="1"/>
+    <col min="21" max="21" width="10.7583333333333" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:21">
+    <row r="1" ht="15.75" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1947,7 +1950,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15" spans="1:21">
+    <row r="2" customFormat="1" ht="15.75" spans="1:21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -2012,7 +2015,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="15" spans="1:19">
+    <row r="3" customFormat="1" ht="15.75" spans="1:19">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -2071,7 +2074,7 @@
         <v>45304</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="15" spans="1:11">
+    <row r="4" customFormat="1" ht="15.75" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -2106,7 +2109,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="15" spans="1:20">
+    <row r="5" customFormat="1" ht="15.75" spans="1:20">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -2166,7 +2169,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" customFormat="1" ht="15" spans="1:20">
+    <row r="6" customFormat="1" ht="15.75" spans="1:20">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -2228,7 +2231,7 @@
         <v>45344</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="15" spans="1:20">
+    <row r="7" customFormat="1" ht="15.75" spans="1:20">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -2315,7 +2318,7 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="15" spans="1:20">
+    <row r="9" customFormat="1" ht="15.75" spans="1:20">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -2377,7 +2380,7 @@
         <v>45263</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="15" spans="1:20">
+    <row r="10" customFormat="1" ht="15.75" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2419,7 +2422,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="15" spans="1:20">
+    <row r="11" customFormat="1" ht="15.75" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2461,7 +2464,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="15" spans="1:20">
+    <row r="12" customFormat="1" ht="15.75" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2485,7 +2488,7 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="1" ht="15" spans="1:20">
+    <row r="13" customFormat="1" ht="15.75" spans="1:20">
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
@@ -2547,7 +2550,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="15" spans="1:20">
+    <row r="14" customFormat="1" ht="15.75" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2571,7 +2574,7 @@
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" customFormat="1" ht="15" spans="1:20">
+    <row r="15" customFormat="1" ht="15.75" spans="1:20">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -2627,7 +2630,7 @@
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" customFormat="1" ht="15" spans="1:20">
+    <row r="16" customFormat="1" ht="15.75" spans="1:20">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -2689,7 +2692,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="15" spans="1:20">
+    <row r="17" customFormat="1" ht="15.75" spans="1:20">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -2751,7 +2754,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="15" spans="1:20">
+    <row r="18" customFormat="1" ht="15.75" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2783,7 +2786,7 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
     </row>
-    <row r="19" customFormat="1" ht="15" spans="1:20">
+    <row r="19" customFormat="1" ht="15.75" spans="1:20">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -2845,7 +2848,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="15" spans="1:20">
+    <row r="20" customFormat="1" ht="15.75" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2877,7 +2880,7 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
     </row>
-    <row r="21" customFormat="1" ht="15" spans="1:20">
+    <row r="21" customFormat="1" ht="15.75" spans="1:20">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -2939,7 +2942,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="15" spans="1:20">
+    <row r="22" customFormat="1" ht="15.75" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2981,7 +2984,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="15" spans="1:20">
+    <row r="23" customFormat="1" ht="15.75" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3013,7 +3016,7 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="15" spans="1:20">
+    <row r="24" customFormat="1" ht="15.75" spans="1:20">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
@@ -3075,7 +3078,7 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="15" spans="1:20">
+    <row r="25" customFormat="1" ht="15.75" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3117,7 +3120,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="15" spans="1:20">
+    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3155,7 +3158,7 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
     </row>
-    <row r="27" customFormat="1" ht="15" spans="1:20">
+    <row r="27" customFormat="1" ht="15.75" spans="1:20">
       <c r="A27" s="6" t="s">
         <v>103</v>
       </c>
@@ -3199,7 +3202,7 @@
       <c r="S27" s="25"/>
       <c r="T27" s="25"/>
     </row>
-    <row r="28" customFormat="1" ht="15" spans="1:20">
+    <row r="28" customFormat="1" ht="15.75" spans="1:20">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -3253,7 +3256,7 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
     </row>
-    <row r="29" customFormat="1" ht="15" spans="1:18">
+    <row r="29" customFormat="1" ht="15.75" spans="1:18">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -3295,7 +3298,7 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
     </row>
-    <row r="30" customFormat="1" ht="15" spans="1:20">
+    <row r="30" customFormat="1" ht="15.75" spans="1:20">
       <c r="A30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3349,7 +3352,7 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" customFormat="1" ht="15" spans="1:20">
+    <row r="31" customFormat="1" ht="15.75" spans="1:20">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -3411,7 +3414,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="15" spans="1:20">
+    <row r="32" customFormat="1" ht="15.75" spans="1:20">
       <c r="A32" s="5" t="s">
         <v>20</v>
       </c>
@@ -3473,7 +3476,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="15" spans="1:20">
+    <row r="33" customFormat="1" ht="15.75" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3501,7 +3504,7 @@
       <c r="S33" s="22"/>
       <c r="T33" s="22"/>
     </row>
-    <row r="34" customFormat="1" ht="15" spans="1:20">
+    <row r="34" customFormat="1" ht="15.75" spans="1:20">
       <c r="A34" s="6" t="s">
         <v>20</v>
       </c>
@@ -3557,7 +3560,7 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
     </row>
-    <row r="35" customFormat="1" ht="15" spans="1:20">
+    <row r="35" customFormat="1" ht="15.75" spans="1:20">
       <c r="A35" s="5" t="s">
         <v>20</v>
       </c>
@@ -3619,7 +3622,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="15" spans="1:20">
+    <row r="36" customFormat="1" ht="15.75" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3661,7 +3664,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="15" spans="1:20">
+    <row r="37" customFormat="1" ht="15.75" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3703,7 +3706,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="15" spans="1:20">
+    <row r="38" customFormat="1" ht="15.75" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3732,7 +3735,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" customFormat="1" ht="15" spans="1:20">
+    <row r="39" customFormat="1" ht="15.75" spans="1:20">
       <c r="A39" s="5" t="s">
         <v>20</v>
       </c>
@@ -3794,7 +3797,7 @@
         <v>45592</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="15" spans="1:20">
+    <row r="40" customFormat="1" ht="15.75" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3836,7 +3839,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="15" spans="1:13">
+    <row r="41" customFormat="1" ht="15.75" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3857,7 +3860,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="15" spans="1:20">
+    <row r="42" customFormat="1" ht="15.75" spans="1:20">
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
@@ -3919,7 +3922,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="15" spans="1:20">
+    <row r="43" customFormat="1" ht="15.75" spans="1:20">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3961,7 +3964,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="15" spans="1:20">
+    <row r="44" customFormat="1" ht="15.75" spans="1:20">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -4039,7 +4042,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
     </row>
-    <row r="46" customFormat="1" ht="15" spans="1:20">
+    <row r="46" customFormat="1" ht="15.75" spans="1:20">
       <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
@@ -4101,7 +4104,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="15" spans="1:20">
+    <row r="47" customFormat="1" ht="15.75" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4143,7 +4146,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="15" spans="1:20">
+    <row r="48" customFormat="1" ht="15.75" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4175,7 +4178,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="15" spans="1:16">
+    <row r="49" s="2" customFormat="1" ht="15.75" spans="1:16">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -4225,7 +4228,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="15" spans="1:20">
+    <row r="50" customFormat="1" ht="15.75" spans="1:20">
       <c r="A50" s="5" t="s">
         <v>20</v>
       </c>
@@ -4287,7 +4290,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="15" spans="1:20">
+    <row r="51" customFormat="1" ht="15.75" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4329,7 +4332,7 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="15" spans="1:20">
+    <row r="52" customFormat="1" ht="15.75" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4371,7 +4374,7 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="15" spans="1:12">
+    <row r="53" customFormat="1" ht="15.75" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>20</v>
       </c>
@@ -4409,7 +4412,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="15" spans="1:20">
+    <row r="54" customFormat="1" ht="15.75" spans="1:20">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4431,7 +4434,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="22"/>
     </row>
-    <row r="55" customFormat="1" ht="15" spans="1:20">
+    <row r="55" customFormat="1" ht="15.75" spans="1:20">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4453,7 +4456,7 @@
       <c r="S55" s="22"/>
       <c r="T55" s="22"/>
     </row>
-    <row r="56" customFormat="1" ht="15" spans="1:20">
+    <row r="56" customFormat="1" ht="15.75" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4475,7 +4478,7 @@
       <c r="S56" s="22"/>
       <c r="T56" s="22"/>
     </row>
-    <row r="57" customFormat="1" ht="15" spans="1:20">
+    <row r="57" customFormat="1" ht="15.75" spans="1:20">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4497,7 +4500,7 @@
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
     </row>
-    <row r="58" customFormat="1" ht="15" spans="1:20">
+    <row r="58" customFormat="1" ht="15.75" spans="1:20">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4519,7 +4522,7 @@
       <c r="S58" s="27"/>
       <c r="T58" s="27"/>
     </row>
-    <row r="59" customFormat="1" ht="15" spans="1:20">
+    <row r="59" customFormat="1" ht="15.75" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4541,7 +4544,7 @@
       <c r="S59" s="27"/>
       <c r="T59" s="27"/>
     </row>
-    <row r="60" customFormat="1" ht="15" spans="1:20">
+    <row r="60" customFormat="1" ht="15.75" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -1742,10 +1742,10 @@
       <c r="K3" s="21">
         <v>46138</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="21">
         <v>46143</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="21">
         <v>46152</v>
       </c>
     </row>

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -1189,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1266,6 +1266,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1728,7 +1731,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:13">
+    <row r="3" ht="15.75" spans="1:14">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1747,6 +1750,9 @@
       </c>
       <c r="M3" s="21">
         <v>46152</v>
+      </c>
+      <c r="N3" s="29">
+        <v>46159</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="15.75"/>
@@ -1787,10 +1793,10 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
     </row>
     <row r="19" ht="18.75" spans="2:13">
       <c r="B19" s="9"/>
@@ -1801,10 +1807,10 @@
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
     </row>
     <row r="20" ht="18.75" spans="2:12">
       <c r="B20" s="9"/>
@@ -1815,8 +1821,8 @@
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
     </row>
     <row r="21" ht="18.75" spans="2:13">
       <c r="B21" s="9"/>
@@ -1827,10 +1833,10 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
     </row>
     <row r="22" ht="18.75" spans="2:13">
       <c r="B22" s="9"/>
@@ -1841,10 +1847,10 @@
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/Sideline/家教带课记录.xlsx
+++ b/Sideline/家教带课记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="25600" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="Doing" sheetId="1" r:id="rId1"/>
@@ -1189,7 +1189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1266,9 +1266,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1593,21 +1590,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="5.375" customWidth="1"/>
-    <col min="3" max="3" width="11.1833333333333" customWidth="1"/>
-    <col min="4" max="4" width="7.875" customWidth="1"/>
+    <col min="1" max="2" width="5.37272727272727" customWidth="1"/>
+    <col min="3" max="3" width="11.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="7.87272727272727" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="6.875" customWidth="1"/>
-    <col min="7" max="7" width="24.2583333333333" customWidth="1"/>
-    <col min="8" max="8" width="6.125" customWidth="1"/>
-    <col min="9" max="9" width="9.125" customWidth="1"/>
-    <col min="10" max="10" width="10.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="6.87272727272727" customWidth="1"/>
+    <col min="7" max="7" width="24.2545454545455" customWidth="1"/>
+    <col min="8" max="8" width="6.12727272727273" customWidth="1"/>
+    <col min="9" max="9" width="9.12727272727273" customWidth="1"/>
+    <col min="10" max="10" width="10.8363636363636" customWidth="1"/>
     <col min="11" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:20">
+    <row r="1" ht="15" spans="1:20">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1669,7 +1666,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15.75" spans="1:20">
+    <row r="2" customFormat="1" ht="15" spans="1:20">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -1731,7 +1728,7 @@
         <v>46131</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:14">
+    <row r="3" ht="15" spans="1:15">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1751,16 +1748,19 @@
       <c r="M3" s="21">
         <v>46152</v>
       </c>
-      <c r="N3" s="29">
+      <c r="N3" s="22">
         <v>46159</v>
       </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="15.75"/>
-    <row r="12" s="2" customFormat="1" ht="15.75"/>
-    <row r="13" s="2" customFormat="1" ht="15.75"/>
-    <row r="14" s="2" customFormat="1" ht="15.75"/>
-    <row r="15" s="2" customFormat="1" ht="15.75"/>
-    <row r="16" s="2" customFormat="1" ht="15.75" spans="1:9">
+      <c r="O3" s="22">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="15"/>
+    <row r="12" s="2" customFormat="1" ht="15"/>
+    <row r="13" s="2" customFormat="1" ht="15"/>
+    <row r="14" s="2" customFormat="1" ht="15"/>
+    <row r="15" s="2" customFormat="1" ht="15"/>
+    <row r="16" s="2" customFormat="1" ht="15" spans="1:9">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -1771,7 +1771,7 @@
       <c r="H16" s="28"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" s="2" customFormat="1" ht="15.75" spans="1:9">
+    <row r="17" s="2" customFormat="1" ht="15" spans="1:9">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -1782,7 +1782,7 @@
       <c r="H17" s="28"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" ht="18.75" spans="2:13">
+    <row r="18" ht="17.5" spans="2:13">
       <c r="B18" s="9" t="s">
         <v>30</v>
       </c>
@@ -1793,12 +1793,12 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-    </row>
-    <row r="19" ht="18.75" spans="2:13">
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+    </row>
+    <row r="19" ht="17.5" spans="2:13">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -1807,12 +1807,12 @@
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-    </row>
-    <row r="20" ht="18.75" spans="2:12">
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+    </row>
+    <row r="20" ht="17.5" spans="2:12">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -1821,10 +1821,10 @@
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-    </row>
-    <row r="21" ht="18.75" spans="2:13">
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+    </row>
+    <row r="21" ht="17.5" spans="2:13">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -1833,12 +1833,12 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-    </row>
-    <row r="22" ht="18.75" spans="2:13">
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+    </row>
+    <row r="22" ht="17.5" spans="2:13">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -1847,10 +1847,10 @@
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1876,22 +1876,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="4.58333333333333" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="17.725" customWidth="1"/>
-    <col min="5" max="5" width="23.1833333333333" customWidth="1"/>
-    <col min="6" max="6" width="7.33333333333333" customWidth="1"/>
-    <col min="7" max="7" width="27.125" customWidth="1"/>
-    <col min="8" max="9" width="9.58333333333333" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="20" width="11.275" customWidth="1"/>
-    <col min="21" max="21" width="10.7583333333333" customWidth="1"/>
+    <col min="1" max="2" width="4.58181818181818" customWidth="1"/>
+    <col min="3" max="3" width="10.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="17.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="23.1818181818182" customWidth="1"/>
+    <col min="6" max="6" width="7.33636363636364" customWidth="1"/>
+    <col min="7" max="7" width="27.1272727272727" customWidth="1"/>
+    <col min="8" max="9" width="9.58181818181818" customWidth="1"/>
+    <col min="10" max="10" width="10.6272727272727" customWidth="1"/>
+    <col min="11" max="20" width="11.2727272727273" customWidth="1"/>
+    <col min="21" max="21" width="10.7545454545455" customWidth="1"/>
     <col min="22" max="23" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:21">
+    <row r="1" ht="15" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="15.75" spans="1:21">
+    <row r="2" customFormat="1" ht="15" spans="1:21">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>45248</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="15.75" spans="1:19">
+    <row r="3" customFormat="1" ht="15" spans="1:19">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>45304</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="15.75" spans="1:11">
+    <row r="4" customFormat="1" ht="15" spans="1:11">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="5" customFormat="1" ht="15.75" spans="1:20">
+    <row r="5" customFormat="1" ht="15" spans="1:20">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" customFormat="1" ht="15.75" spans="1:20">
+    <row r="6" customFormat="1" ht="15" spans="1:20">
       <c r="A6" s="5" t="s">
         <v>39</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>45344</v>
       </c>
     </row>
-    <row r="7" customFormat="1" ht="15.75" spans="1:20">
+    <row r="7" customFormat="1" ht="15" spans="1:20">
       <c r="A7" s="6" t="s">
         <v>20</v>
       </c>
@@ -2324,7 +2324,7 @@
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
     </row>
-    <row r="9" customFormat="1" ht="15.75" spans="1:20">
+    <row r="9" customFormat="1" ht="15" spans="1:20">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>45263</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="15.75" spans="1:20">
+    <row r="10" customFormat="1" ht="15" spans="1:20">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2428,7 +2428,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="11" customFormat="1" ht="15.75" spans="1:20">
+    <row r="11" customFormat="1" ht="15" spans="1:20">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2470,7 +2470,7 @@
         <v>45445</v>
       </c>
     </row>
-    <row r="12" customFormat="1" ht="15.75" spans="1:20">
+    <row r="12" customFormat="1" ht="15" spans="1:20">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2494,7 +2494,7 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="1" ht="15.75" spans="1:20">
+    <row r="13" customFormat="1" ht="15" spans="1:20">
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>45453</v>
       </c>
     </row>
-    <row r="14" customFormat="1" ht="15.75" spans="1:20">
+    <row r="14" customFormat="1" ht="15" spans="1:20">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2580,7 +2580,7 @@
       <c r="S14" s="17"/>
       <c r="T14" s="19"/>
     </row>
-    <row r="15" customFormat="1" ht="15.75" spans="1:20">
+    <row r="15" customFormat="1" ht="15" spans="1:20">
       <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
@@ -2636,7 +2636,7 @@
       <c r="S15" s="17"/>
       <c r="T15" s="19"/>
     </row>
-    <row r="16" customFormat="1" ht="15.75" spans="1:20">
+    <row r="16" customFormat="1" ht="15" spans="1:20">
       <c r="A16" s="6" t="s">
         <v>20</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="17" customFormat="1" ht="15.75" spans="1:20">
+    <row r="17" customFormat="1" ht="15" spans="1:20">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>45400</v>
       </c>
     </row>
-    <row r="18" customFormat="1" ht="15.75" spans="1:20">
+    <row r="18" customFormat="1" ht="15" spans="1:20">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2792,7 +2792,7 @@
       <c r="S18" s="17"/>
       <c r="T18" s="17"/>
     </row>
-    <row r="19" customFormat="1" ht="15.75" spans="1:20">
+    <row r="19" customFormat="1" ht="15" spans="1:20">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>45451</v>
       </c>
     </row>
-    <row r="20" customFormat="1" ht="15.75" spans="1:20">
+    <row r="20" customFormat="1" ht="15" spans="1:20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2886,7 +2886,7 @@
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
     </row>
-    <row r="21" customFormat="1" ht="15.75" spans="1:20">
+    <row r="21" customFormat="1" ht="15" spans="1:20">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>45311</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="15.75" spans="1:20">
+    <row r="22" customFormat="1" ht="15" spans="1:20">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2990,7 +2990,7 @@
         <v>45423</v>
       </c>
     </row>
-    <row r="23" customFormat="1" ht="15.75" spans="1:20">
+    <row r="23" customFormat="1" ht="15" spans="1:20">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3022,7 +3022,7 @@
       <c r="S23" s="19"/>
       <c r="T23" s="19"/>
     </row>
-    <row r="24" customFormat="1" ht="15.75" spans="1:20">
+    <row r="24" customFormat="1" ht="15" spans="1:20">
       <c r="A24" s="5" t="s">
         <v>20</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>45325</v>
       </c>
     </row>
-    <row r="25" customFormat="1" ht="15.75" spans="1:20">
+    <row r="25" customFormat="1" ht="15" spans="1:20">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3126,7 +3126,7 @@
         <v>45354</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="15.75" spans="1:20">
+    <row r="26" s="1" customFormat="1" ht="15" spans="1:20">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3164,7 +3164,7 @@
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
     </row>
-    <row r="27" customFormat="1" ht="15.75" spans="1:20">
+    <row r="27" customFormat="1" ht="15" spans="1:20">
       <c r="A27" s="6" t="s">
         <v>103</v>
       </c>
@@ -3208,7 +3208,7 @@
       <c r="S27" s="25"/>
       <c r="T27" s="25"/>
     </row>
-    <row r="28" customFormat="1" ht="15.75" spans="1:20">
+    <row r="28" customFormat="1" ht="15" spans="1:20">
       <c r="A28" s="6" t="s">
         <v>20</v>
       </c>
@@ -3262,7 +3262,7 @@
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
     </row>
-    <row r="29" customFormat="1" ht="15.75" spans="1:18">
+    <row r="29" customFormat="1" ht="15" spans="1:18">
       <c r="A29" s="6" t="s">
         <v>20</v>
       </c>
@@ -3304,7 +3304,7 @@
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
     </row>
-    <row r="30" customFormat="1" ht="15.75" spans="1:20">
+    <row r="30" customFormat="1" ht="15" spans="1:20">
       <c r="A30" s="6" t="s">
         <v>116</v>
       </c>
@@ -3358,7 +3358,7 @@
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
-    <row r="31" customFormat="1" ht="15.75" spans="1:20">
+    <row r="31" customFormat="1" ht="15" spans="1:20">
       <c r="A31" s="6" t="s">
         <v>20</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="32" customFormat="1" ht="15.75" spans="1:20">
+    <row r="32" customFormat="1" ht="15" spans="1:20">
       <c r="A32" s="5" t="s">
         <v>20</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>45627</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="15.75" spans="1:20">
+    <row r="33" customFormat="1" ht="15" spans="1:20">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3510,7 +3510,7 @@
       <c r="S33" s="22"/>
       <c r="T33" s="22"/>
     </row>
-    <row r="34" customFormat="1" ht="15.75" spans="1:20">
+    <row r="34" customFormat="1" ht="15" spans="1:20">
       <c r="A34" s="6" t="s">
         <v>20</v>
       </c>
@@ -3566,7 +3566,7 @@
       <c r="S34" s="17"/>
       <c r="T34" s="17"/>
     </row>
-    <row r="35" customFormat="1" ht="15.75" spans="1:20">
+    <row r="35" customFormat="1" ht="15" spans="1:20">
       <c r="A35" s="5" t="s">
         <v>20</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>45670</v>
       </c>
     </row>
-    <row r="36" customFormat="1" ht="15.75" spans="1:20">
+    <row r="36" customFormat="1" ht="15" spans="1:20">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3670,7 +3670,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="37" customFormat="1" ht="15.75" spans="1:20">
+    <row r="37" customFormat="1" ht="15" spans="1:20">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3712,7 +3712,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="38" customFormat="1" ht="15.75" spans="1:20">
+    <row r="38" customFormat="1" ht="15" spans="1:20">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3741,7 +3741,7 @@
       <c r="S38" s="22"/>
       <c r="T38" s="22"/>
     </row>
-    <row r="39" customFormat="1" ht="15.75" spans="1:20">
+    <row r="39" customFormat="1" ht="15" spans="1:20">
       <c r="A39" s="5" t="s">
         <v>20</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>45592</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="15.75" spans="1:20">
+    <row r="40" customFormat="1" ht="15" spans="1:20">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3845,7 +3845,7 @@
         <v>45718</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="15.75" spans="1:13">
+    <row r="41" customFormat="1" ht="15" spans="1:13">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3866,7 +3866,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="15.75" spans="1:20">
+    <row r="42" customFormat="1" ht="15" spans="1:20">
       <c r="A42" s="5" t="s">
         <v>20</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>45623</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="15.75" spans="1:20">
+    <row r="43" customFormat="1" ht="15" spans="1:20">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3970,7 +3970,7 @@
         <v>45703</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="15.75" spans="1:20">
+    <row r="44" customFormat="1" ht="15" spans="1:20">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -4048,7 +4048,7 @@
       <c r="S45" s="22"/>
       <c r="T45" s="22"/>
     </row>
-    <row r="46" customFormat="1" ht="15.75" spans="1:20">
+    <row r="46" customFormat="1" ht="15" spans="1:20">
       <c r="A46" s="5" t="s">
         <v>20</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>45620</v>
       </c>
     </row>
-    <row r="47" customFormat="1" ht="15.75" spans="1:20">
+    <row r="47" customFormat="1" ht="15" spans="1:20">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -4152,7 +4152,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="48" customFormat="1" ht="15.75" spans="1:20">
+    <row r="48" customFormat="1" ht="15" spans="1:20">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -4184,7 +4184,7 @@
       <c r="S48" s="22"/>
       <c r="T48" s="22"/>
     </row>
-    <row r="49" s="2" customFormat="1" ht="15.75" spans="1:16">
+    <row r="49" s="2" customFormat="1" ht="15" spans="1:16">
       <c r="A49" s="2" t="s">
         <v>20</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" customFormat="1" ht="15.75" spans="1:20">
+    <row r="50" customFormat="1" ht="15" spans="1:20">
       <c r="A50" s="5" t="s">
         <v>20</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>45746</v>
       </c>
     </row>
-    <row r="51" customFormat="1" ht="15.75" spans="1:20">
+    <row r="51" customFormat="1" ht="15" spans="1:20">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -4338,7 +4338,7 @@
         <v>45787</v>
       </c>
     </row>
-    <row r="52" customFormat="1" ht="15.75" spans="1:20">
+    <row r="52" customFormat="1" ht="15" spans="1:20">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -4380,7 +4380,7 @@
         <v>45822</v>
       </c>
     </row>
-    <row r="53" customFormat="1" ht="15.75" spans="1:12">
+    <row r="53" customFormat="1" ht="15" spans="1:12">
       <c r="A53" s="5" t="s">
         <v>20</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="54" customFormat="1" ht="15.75" spans="1:20">
+    <row r="54" customFormat="1" ht="15" spans="1:20">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4440,7 +4440,7 @@
       <c r="S54" s="22"/>
       <c r="T54" s="22"/>
     </row>
-    <row r="55" customFormat="1" ht="15.75" spans="1:20">
+    <row r="55" customFormat="1" ht="15" spans="1:20">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4462,7 +4462,7 @@
       <c r="S55" s="22"/>
       <c r="T55" s="22"/>
     </row>
-    <row r="56" customFormat="1" ht="15.75" spans="1:20">
+    <row r="56" customFormat="1" ht="15" spans="1:20">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4484,7 +4484,7 @@
       <c r="S56" s="22"/>
       <c r="T56" s="22"/>
     </row>
-    <row r="57" customFormat="1" ht="15.75" spans="1:20">
+    <row r="57" customFormat="1" ht="15" spans="1:20">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4506,7 +4506,7 @@
       <c r="S57" s="22"/>
       <c r="T57" s="22"/>
     </row>
-    <row r="58" customFormat="1" ht="15.75" spans="1:20">
+    <row r="58" customFormat="1" ht="15" spans="1:20">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4528,7 +4528,7 @@
       <c r="S58" s="27"/>
       <c r="T58" s="27"/>
     </row>
-    <row r="59" customFormat="1" ht="15.75" spans="1:20">
+    <row r="59" customFormat="1" ht="15" spans="1:20">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -4550,7 +4550,7 @@
       <c r="S59" s="27"/>
       <c r="T59" s="27"/>
     </row>
-    <row r="60" customFormat="1" ht="15.75" spans="1:20">
+    <row r="60" customFormat="1" ht="15" spans="1:20">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
